--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260923.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260923.xlsx
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>12,693,000</t>
+          <t>11,279,100</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>11,279,100</t>
+          <t>3,521,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>3,521,000</t>
+          <t>12,693,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>16,273,000</t>
+          <t>16,031,073</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>16,031,073</t>
+          <t>16,273,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>2,937,000</t>
+          <t>1,973,678</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,973,678</t>
+          <t>2,937,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
